--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0041.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0041.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Camp Overwatch</t>
+          <t>Giám Sát Trại</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Withering Frontline</t>
+          <t>Tiền Tuyến Khô Héo</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Misty Coast</t>
+          <t>Bờ Biển Sương Khói</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Rearguard Base</t>
+          <t>Căn Cứ Hậu Phương</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Tường vô hình cho khu vực Desorock trong Chương I và II@ Nhiệm vụ chính</t>
+          <t>Bức Tường Vô Hình khu vực Desorock Chương I &amp; II@ Nhiệm Vụ Chính</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Settle Range</t>
+          <t>Phạm Vi Giải Quyết</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Donglu Nghiên cứu Station</t>
+          <t>Trạm Nghiên cứu Donglu</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Nostalgia Isle</t>
+          <t>Đảo Hoài Cổ</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Khu Vực Incinero Petal - Căn Cứ West Range</t>
+          <t>Khu Vực Cánh Tây - Đốt Cánh Hoa Incinero</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Sea of Flames Area</t>
+          <t>Khu Vực Biển Lửa</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Base Incinero Petal Area</t>
+          <t>Khu Vực Cánh Lửa Incinero Cơ Bản</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Rừng Tối</t>
+          <t>Dim Forest</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Wenye Beach</t>
+          <t>Bãi Biển Wenye</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Violet Banyan</t>
+          <t>Cây Đa Tím</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Giant Banyan</t>
+          <t>Cây Đa Khổng Lồ</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Forbidden Forest</t>
+          <t>Rừng Cấm Địa</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Thorny Passage</t>
+          <t>Lối Đi Gai Góc</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Corroded Ruins</t>
+          <t>Tàn Dư Bị Ăn Mòn</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Hermit Settlement</t>
+          <t>Khu Định Cư Ẩn Sĩ</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Remnant Residence</t>
+          <t>Nơi Ở Dư</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Challenge Invisible Walls</t>
+          <t>Thử Thách Tường Ảo</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Vault Underground</t>
+          <t>Hầm Ngầm Kho Báu</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Tháp Bỏ Hoang</t>
+          <t>Tháp Bị Bỏ Rơi</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Precious Metals and Artworks Depository</t>
+          <t>Kho tàng Kim loại &amp; Tác phẩm Nghệ thuật</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Unknown Vault Area</t>
+          <t>Khu Vực Kho Ngầm Lạ</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Echo Depository</t>
+          <t>Kho Tiếng Vọng</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Echo Station</t>
+          <t>Trạm Echo</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Precious Metals and Artworks Depository - Tầng 1</t>
+          <t>Kho tàng Kim loại &amp; Tác phẩm Nghệ thuật - Tầng 1</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Precious Metals and Artworks Depository - Tầng 2</t>
+          <t>Kho tàng Kim loại &amp; Tác phẩm Nghệ thuật - Tầng 2</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Precious Metals and Artworks Depository - Tầng 3</t>
+          <t>Kho tàng Kim loại &amp; Tác phẩm Nghệ thuật - Tầng 3</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Precious Metals and Artworks Depository - Tầng 4</t>
+          <t>Kho tàng Kim loại &amp; Tác phẩm Nghệ thuật - Tầng 4</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Echo Depository 1st Floor</t>
+          <t>Tầng 1 Kho Tiếng Vọng</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Echo Depository 2nd Floor</t>
+          <t>Tầng 2 Kho Tiếng Vọng</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Echo Depository 3rd Floor</t>
+          <t>Tầng 3 Kho Lưu Trữ Tiếng Vọng</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Echo Depository 4th Floor</t>
+          <t>Tầng 4 Kho Lưu Trữ Tiếng Vọng</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Underground Level 1</t>
+          <t>Tầng Dưới Lòng Đất 1</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Underground Level 2</t>
+          <t>Tầng Dưới Lòng Đất 2</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>A Hidden Place</t>
+          <t>Nơi Ẩn Mình</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Echo Station Interior</t>
+          <t>Nội Thất Trạm Echo</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Unknown Vault Area Interior</t>
+          <t>Bên Trong Kho Ngầm Lạ</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Riccioli Islands</t>
+          <t>Quần Đảo Riccioli</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Port of Riccioli</t>
+          <t>Cảng Riccioli</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Helm Village</t>
+          <t>Làng Helm</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Serene Bay</t>
+          <t>Vịnh Thanh Bình</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Reyes Ruins</t>
+          <t>Tàn Tích Reyes</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Drake's Island</t>
+          <t>Đảo Drake</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Fallen Grave</t>
+          <t>Mộ Hoang Tàn</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Anima Cradle</t>
+          <t>Cái Nôi Sinh Mệnh</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Energy Hub</t>
+          <t>Trung Tâm Năng Lượng</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Sanctuary of Faith</t>
+          <t>Thánh Địa Niềm Tin</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Lumen Tower</t>
+          <t>Tháp Lumen</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Energy Hub Lower Tier</t>
+          <t>Tầng Dưới Trạm Năng Lượng</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Vực Sâu Cõi Ảo Ảnh</t>
+          <t>Vực Sâu Cõi Ảo</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Breath Alloy</t>
+          <t>Hợp Kim Hơi Thở</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Freezing Alloy</t>
+          <t>Hợp Kim Đông Cứng</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Rapido Alloy</t>
+          <t>Hợp Kim Rapido</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Striking Alloy</t>
+          <t>Hợp Kim Đòn Đánh</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Intimidating Alloy</t>
+          <t>Hợp Kim Uy Hiếp</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Deafening Alloy</t>
+          <t>Hợp Kim Đinh Tai</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Furious Alloy</t>
+          <t>Hợp Kim Cuồng Nộ</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Ethereal Alloy</t>
+          <t>Hợp Kim Siêu Nhiên</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Everlasting Alloy</t>
+          <t>Hợp Kim Vĩnh Cửu</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Points Rules</t>
+          <t>Quy Tắc Điểm</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Lone Mourning Aix</t>
+          <t>Aix Tang Lễ Cô Đơn</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Phát hiện dao động năng lượng bất thường phía trước</t>
+          <t>Phát hiện dao động năng lượng bất thường phía trước!</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Corroded Memory Zones</t>
+          <t>Vùng Ký Ức Bị Ăn Mòn</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Crownless - True</t>
+          <t>Crownless - Bản Chính</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Địa Điểm Cúng Dâng</t>
+          <t>Địa Điểm Dâng Hiến</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Tháp Bỏ Hoang</t>
+          <t>Tháp Bị Bỏ Rơi</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Truthseeker's Pass: Upper Tier</t>
+          <t>Thẻ Thông Hành Của Kẻ Tầm Sự Thật: Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Truthseeker's Pass: Middle Tier</t>
+          <t>Thẻ Thông Hành Của Kẻ Tầm Sự Thật: Hạng Trung Cấp</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Truthseeker's Pass: Lower Tier</t>
+          <t>Thẻ Thông Hành Của Kẻ Tầm Sự Thật: Hạng Cơ Bản</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Luminous Shore</t>
+          <t>Bờ Biển Lấp Lánh</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Xuanji Ridges</t>
+          <t>Mạch Huyền Cơ</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Tianqu Tree</t>
+          <t>Thụ Thiên Khúc</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Loong's Ridge</t>
+          <t>Dãy Núi của Loong</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Loong's Crest</t>
+          <t>Huy Hiệu Rồng</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Woodveil Hall: Upper Tier</t>
+          <t>Đại Sảnh Woodveil: Tầng Trên</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Woodveil Hall: Middle Tier</t>
+          <t>Đại Sảnh Woodveil: Tầng Giữa</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Woodveil Hall: Lower Tier</t>
+          <t>Đại Sảnh Woodveil: Tầng Dưới</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Mianloong Chamber: Upper Tier</t>
+          <t>Khu Vực Mianloong: Tầng Trên</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Mianloong Chamber: Lower Tier</t>
+          <t>Khu Vực Mianloong: Tầng Dưới</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Chòm Sao Trong Khung Cửa Thời Gian</t>
+          <t>Chòm sao trong Khẩu Độ Thời Gian</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Phòng Trưng Bày Tro Tàn</t>
+          <t>Phòng Trưng bày Tro Đen</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>The Fated Confrontation</t>
+          <t>Cuộc Đối Đầu Định Mệnh</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Cục An Ninh Công Cộng Hearing Room</t>
+          <t>Phòng Thẩm Vấn Cục An Ninh Công Cộng</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Wooly Kingdom</t>
+          <t>Vương Quốc Lông Xù</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Wooly Kingdom</t>
+          <t>Vương Quốc Lông Xù</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Hành Lang Đau Khổ</t>
+          <t>Hành Lang Thống Khổ</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Summer Violets</t>
+          <t>Hoa Tím Mùa Hạ</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Deepsky Stargate</t>
+          <t>Cổng Vũ Trụ DeepSky</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Deepsky Stargate</t>
+          <t>Cổng Vũ Trụ DeepSky</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Deepsky Stargate</t>
+          <t>Cổng Vũ Trụ DeepSky</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Onslaught</t>
+          <t>Tấn công dữ dội</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Swift Attack</t>
+          <t>Tấn Công Nhanh</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Coordination</t>
+          <t>Điều Phối</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Casualty</t>
+          <t>Thương Vong</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Động lực</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Confrontation</t>
+          <t>Đối Đầu</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Harmony</t>
+          <t>Hòa Điệu</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Immaculate</t>
+          <t>Hoàn hảo</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Clobber</t>
+          <t>Đập tan</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Rumble</t>
+          <t>Ầm ầm</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Refraction</t>
+          <t>Khúc xạ</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Accompaniment</t>
+          <t>Đệm nhạc</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Whirl</t>
+          <t>Xoáy Cuộn</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Reverberance</t>
+          <t>Dư Âm</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Blaze</t>
+          <t>Lửa Thiêu</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Động lực</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Confrontation</t>
+          <t>Đối Đầu</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Immaculate</t>
+          <t>Hoàn hảo</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Zeal</t>
+          <t>Nhiệt Huyết</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Breeze</t>
+          <t>Cơn Gió Nhẹ</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Harmony</t>
+          <t>Hòa Điệu</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Liệu Echoid Có Mơ Về Cừu Điện Không?</t>
+          <t>Liệu Echo Có Mơ Về Cừu Điện Không?</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Hypnotic Image</t>
+          <t>Ảo Ảnh Thôi Miên</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Light Sleep</t>
+          <t>Giấc Ngủ Nhẹ</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Languid Frequency</t>
+          <t>Tần Số Lười Biếng</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Altered Rhythm</t>
+          <t>Nhịp Điệu Biến Đổi</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Sinister Empathy</t>
+          <t>Đồng Cảm U Minh</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Daylit Mirage</t>
+          <t>Ảo Ảnh Ban Ngày</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Mô phỏng Chiến đấu Vô tận</t>
+          <t>Mô Phỏng Chiến Đấu Vô Tận</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Dự báo thời tiết Solaris</t>
+          <t>Dự báo Thời tiết Solaris</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Detection Point I</t>
+          <t>Điểm Phát Hiện I</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Detection Point II</t>
+          <t>Điểm Phát Hiện II</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Detection Point III</t>
+          <t>Điểm Phát Hiện III</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Detection Point IV</t>
+          <t>Điểm Phát Hiện IV</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Detection Point V</t>
+          <t>Điểm Phát Hiện V</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Detection Point VI</t>
+          <t>Điểm Phát Hiện VI</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Detection Point VII</t>
+          <t>Điểm Phát Hiện VII</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Winds of Departure</t>
+          <t>Gió Lìa Xa</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Golden Brick Road</t>
+          <t>Con Đường Gạch Vàng</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Emerald Realm</t>
+          <t>Vùng Ngọc Lục Bảo</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Castle of Darkness</t>
+          <t>Lâu Đài Bóng Tối</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Rustic Cottage</t>
+          <t>Ngôi Nhà Gỗ Cũ</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Over the Rainbow</t>
+          <t>Bên Kia Cầu Vồng</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Lottie Lost with a Parasol</t>
+          <t>Lottie Lost với Ô Dù</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Starry Night Over Ragunna</t>
+          <t>Đêm Sao Trên Ragunna</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Vitreum Dancer's Smile</t>
+          <t>Nụ Cười Vũ Công Pha Lê</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Người Hành Hương Trong Biển Sương Mù</t>
+          <t>Lữ Khách Trong Biển Sương Mù</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Acolyte Với Bông Tai Ngọc Trai</t>
+          <t>Tín Đồ Đeo Hoa Tai Ngọc Trai</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Faith Leading the People</t>
+          <t>Niềm Tin Dẫn Lối Nhân Dân</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>The Birth of Imperator</t>
+          <t>Sự Ra Đời Của Imperator</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Cái kết của câu chuyện cổ tích</t>
+          <t>Hồi Kết Của Truyện Cổ Tích</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Mô phỏng Chiến đấu Vô tận</t>
+          <t>Mô Phỏng Chiến Đấu Vô Tận</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Guide Unlocked</t>
+          <t>Đã Mở Khóa Hướng Dẫn</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Current:</t>
+          <t>Hiện tại:</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Collection Progress:</t>
+          <t>Tiến Độ Sưu Tập:</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Chưa Có Dữ Liệu</t>
+          <t>Chưa có dữ liệu</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Velocity Oscillator</t>
+          <t>Dao Động Vận Tốc</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Elution Oscillator</t>
+          <t>Dao Động Hòa Tan</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Pinnacle Oscillator</t>
+          <t>Dao Động Đỉnh Cao</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Fury Oscillator</t>
+          <t>Dao Động Phẫn Nộ</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Roaring Oscillator</t>
+          <t>Dao Động Gầm Thét</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Suspension Transponder</t>
+          <t>Bộ Truyền Tải Lơ Lửng</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Burst-Fire Transponder</t>
+          <t>Bộ Truyền Tín Bùng Cháy</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Delay-Fire Transponder</t>
+          <t>Bộ truyền tín hiệu trì hoãn nổ</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Roaming Transponder</t>
+          <t>Bộ Truyền Tín Lang Thang</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Volley-Fire Transponder</t>
+          <t>Bộ Truyền Tín Phóng Đạn</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Chafing Transponder</t>
+          <t>Bộ Phát Tần Số Cọ Xát</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Speeding Transponder</t>
+          <t>Bộ Truyền Tín Tốc Độ</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Spurring Transponder</t>
+          <t>Bộ Kích Hoạt Tăng Tốc</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Rumbling Transponder</t>
+          <t>Bộ Khuếch Đại Âm Thanh</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Velocity Transponder</t>
+          <t>Bộ Truyền Tín Hiệu Vận Tốc</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>High-Capacity Variable</t>
+          <t>Biến Số Dung Lượng Cao</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Low-Capacity Variable</t>
+          <t>Biến Số Dung Lượng Thấp</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Lên Cấp</t>
+          <t>Nâng cấp Nhiệm vụ</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Raven Field: Challenge</t>
+          <t>Khu Vực Raven: Thử Thách</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Path of Thorn: Challenge</t>
+          <t>Con Đường Gai: Thử Thách</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Rusted Wasteland: Challenge</t>
+          <t>Vùng Đất Hoang Tàn Gỉ Sét: Thử Thách</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Palace of Illusion: Challenge</t>
+          <t>Cung Ảo Ảnh: Thử Thách</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Barren Pasture: Challenge</t>
+          <t>Thử Thách: Đồng Cỏ Cằn Cỗi</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Commencement: Challenge</t>
+          <t>Bắt đầu: Thử thách</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Blazing Cutlass</t>
+          <t>Dao Lửa Blaze</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Cyclone Swarm</t>
+          <t>Bầy Xoáy Lốc</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Tambourine Duo</t>
+          <t>Bộ Đôi Tambourine</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Alptop Champion</t>
+          <t>Nhà Vô Địch Alptop</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Thử thách Chiến thuật của Yhoran</t>
+          <t>Thử Thách Chiến Thuật Yhoran</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Goal 1: Dodge 1 attack</t>
+          <t>Mục tiêu 1: Né 1 đòn tấn công</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Hất ngã Hoartoise 6 lần</t>
+          <t>Mục tiêu 2: Lật ngửa Hoartoise 6 lần</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Finish thử thách với ít nhất 30 giây còn lại</t>
+          <t>Mục tiêu 3: Hoàn thành thử thách còn ít nhất 30 giây</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Goal 1: Perform 2 Dodge Counters</t>
+          <t>Mục tiêu 1: Thực hiện 2 Né Phản Công</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Finish thử thách với ít nhất 30 giây còn lại</t>
+          <t>Mục tiêu 3: Hoàn thành thử thách còn ít nhất 30 giây</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Đánh bại Prism bằng Violet-Feathered Heron hoặc Cyan-Feathered Heron</t>
+          <t>Mục tiêu 2: Defeat the Prisms via Violet-Feathered Heron or Cyan-Feathered Heron</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Đánh bại tất cả Prism trong vòng 45 giây</t>
+          <t>Mục tiêu 3: Tiêu diệt tất cả Lăng Kính trong vòng 45 giây</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Goal 1: Perform 3 Dodge Counters</t>
+          <t>Mục tiêu 1: Thực hiện 3 Né Phản Công</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Buộc Excarat nổi lên bằng Plunging Attack 3 lần</t>
+          <t>Mục tiêu 2: Ép 3 Excarat trồi lên mặt đất bằng Đòn Lao Dốc 3 lần</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Đánh bại Sabyr Boar cuối cùng</t>
+          <t>Mục tiêu 3: Hạ gục Sabyr Boar sau cùng</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Goal 1: Dodge 3 attacks</t>
+          <t>Mục tiêu 1: Né 3 đòn tấn công</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Tránh bị bất động bởi Traffic Illuminator</t>
+          <t>Mục tiêu 2: Avoid being immobilized by the Traffic Illuminator</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Finish thử thách với ít nhất 60 giây còn lại</t>
+          <t>Mục tiêu 3: Hoàn thành thử thách còn ít nhất 60 giây</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Goal 1: Perform 2 Dodge Counters</t>
+          <t>Mục tiêu 1: Thực hiện 2 Né Phản Công</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Nhận ít hơn 10 đòn đánh</t>
+          <t>Mục tiêu 2: Nhận ít hơn 10 đòn tấn công</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Đánh bại cả hai Glacio Dreadmane trong vòng 20 giây sau khi kẻ đầu tiên bị hạ</t>
+          <t>Mục tiêu 2: Tiêu diệt cả hai Glacio Dreadmane trong vòng 20 giây sau khi con đầu tiên bị hạ</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Finish thử thách với ít nhất 30 giây còn lại</t>
+          <t>Mục tiêu 3: Hoàn thành thử thách còn ít nhất 30 giây</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Dream Patrol: Twin Swords of Light</t>
+          <t>Tuần Tra Giấc Mộng: Song Kiếm Ánh Sáng</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Battle Rank S trở lên trong 10 giây</t>
+          <t>Mục tiêu 1: Duy trì Cấp Độ Chiến Đấu S trở lên trong 10 giây</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Goal 2: Perform 8 Dodges</t>
+          <t>Mục tiêu 2: Né 8 lần</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Dream Patrol: Deadly Ballet</t>
+          <t>Tuần Tra Giấc Mơ: Vũ Điệu Tử Thần</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Battle Rank S trở lên trong 8 giây</t>
+          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu S trở lên trong 8 giây</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Goal 2: Perform 3 Counterattacks</t>
+          <t>Mục tiêu 2: Thực hiện 3 phản công</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Goal 3: Perform 6 Dodge Counters</t>
+          <t>Mục tiêu 3: Phản đòn né tránh 6 lần</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Dream Patrol: Dear Plushie Bạn bè</t>
+          <t>Tuần Tra Giấc Mơ: Những Người Bạn Gấu Bông Thân Yêu</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Battle Rank SS</t>
+          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu SS</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Nhận ít hơn 3 đòn từ Diggy Duggy bay do Cuddle Wuddle Dodgem</t>
+          <t>Mục tiêu 2: Nhận ít hơn 3 đòn từ Diggy Duggy bay do Cuddle Wuddle ném</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Dream Patrol: Averardo Vault</t>
+          <t>Tuần Tra Giấc Mơ: Kho Báu Averardo</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Cứu Dreamscape Nexus khỏi bị phá hủy</t>
+          <t>Mục tiêu 1: Bảo vệ Nexus Cảnh Mộng khỏi bị phá hủy</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Giữ Dreamscape Nexus Integrity trên 30%</t>
+          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 30%</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Giữ Dreamscape Nexus Integrity trên 60%</t>
+          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 60%</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Dream Patrol: Knight in a Storm</t>
+          <t>Tuần Tra Giấc Mơ: Kỵ Sĩ Trong Bão Tố</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Battle Rank S trong hơn 10 giây</t>
+          <t>Mục tiêu 1: Duy trì Cấp Chiến Đấu S trên 10 giây</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Thực hiện 3 đòn phản công làm gián đoạn nâng cấp vũ khí của Knight</t>
+          <t>Mục tiêu 2: Thực hiện 3 phản công làm gián đoạn tăng cường vũ khí của Knight</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Dream Patrol: An Eye for an Eye</t>
+          <t>Tuần Tra Giấc Mơ: Mắt Đền Mắt</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Battle Rank S khi thử thách kết thúc</t>
+          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu S khi thử thách kết thúc</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Ngắt trạng thái tích năng của Roseshroom bằng cách bắn nó</t>
+          <t>Mục tiêu 2: Interrupt the Roseshroom's charging state by shooting it</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Dream Patrol: Haunting Circus</t>
+          <t>Tuần Tra Giấc Mơ: Rạp Xiếc U Minh</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Hạng Chiến Đấu S trở lên trong 8 giây</t>
+          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu S trở lên trong 8 giây</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Không bị trúng vụ nổ Fae Ignis</t>
+          <t>Mục tiêu 2: Don't get caught in the Fae Ignis explosion</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Defeat Chop Chop last</t>
+          <t>Mục tiêu 3: Hạ gục Chop Chop sau cùng</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Dream Patrol: Fagaceae Peninsula</t>
+          <t>Tuần Tra Giấc Mơ: Bán Đảo Fagaceae</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Giải cứu Dreamscape Nexus khỏi sự hủy diệt</t>
+          <t>Mục tiêu 1: Bảo vệ Nexus Cảnh Mộng khỏi bị phá hủy</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Giữ Độ Nguyên Vẹn Dreamscape Nexus trên 30%</t>
+          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 30%</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Giữ Độ Nguyên Vẹn Dreamscape Nexus trên 60%</t>
+          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 60%</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Dream Patrol: Knight of Regrets</t>
+          <t>Tuần Tra Giấc Mơ: Kỵ Sĩ Đầy Hối Tiếc</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Hạng Chiến Đấu S trở lên trong 8 giây</t>
+          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu S trở lên trong 8 giây</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Đánh bại Knight trước khi chúng thực hiện 3 lần nâng cấp vũ khí</t>
+          <t>Mục tiêu 2: Tiêu diệt Knight trước khi hắn nâng cấp vũ khí 3 lần</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Chịu ít hơn 10 đòn đánh</t>
+          <t>Mục tiêu 3: Chịu ít hơn 10 đòn tấn công</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Dream Patrol: Lord of the Windmill</t>
+          <t>Tuần Tra Giấc Mộng: Lãnh Chúa Cối Xay Gió</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Hạng Chiến Đấu SS</t>
+          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu SS</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Chịu ít hơn 6 đòn đánh</t>
+          <t>Mục tiêu 3: Nhận ít hơn 6 đòn</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Dream Patrol: Professional Guard</t>
+          <t>Tuần Tra Giấc Mộng: Vệ Binh Chuyên Nghiệp</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Hạng Chiến Đấu SS khi thử thách kết thúc</t>
+          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu SS khi thử thách kết thúc</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Chịu ít hơn 8 đòn đánh từ Cuddle Wuddle</t>
+          <t>Mục tiêu 3: Nhận ít hơn 8 đòn từ Cuddle Wuddle</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Dream Patrol: Gaze of the Evil</t>
+          <t>Tuần Tra Giấc Mơ: Ánh Mắt Ác Quỷ</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Hạng Chiến Đấu S trở lên trong 8 giây</t>
+          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu S trở lên trong 8 giây</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Goal 3: Perform 6 Dodge Counters</t>
+          <t>Mục tiêu 3: Phản đòn né tránh 6 lần</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Dream Patrol: Whisperwind Haven</t>
+          <t>Tuần Tra Giấc Mộng: Whisperwind Haven</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Giải cứu Dreamscape Nexus khỏi sự hủy diệt</t>
+          <t>Mục tiêu 1: Bảo vệ Nexus Cảnh Mộng khỏi bị phá hủy</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Giữ Độ Nguyên Vẹn Dreamscape Nexus trên 30%</t>
+          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 30%</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Giữ Độ Nguyên Vẹn Dreamscape Nexus trên 60%</t>
+          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 60%</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Dream Patrol: Code of the Deepsea</t>
+          <t>Tuần Tra Giấc Mơ: Bộ Luật Vực Sâu</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Hạng Chiến Đấu S trở lên trong 6 giây</t>
+          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu S trở lên trong 6 giây</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Đánh bại 2 Abyssal Patricius liên tiếp trong vòng 10 giây</t>
+          <t>Mục tiêu 2: Tiêu diệt liên tiếp 2 Abyssal Patricius trong vòng 10 giây</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Bị Frozen dưới 2 lần</t>
+          <t>Mục tiêu 3: Bị đóng băng dưới 2 lần</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Dream Patrol: Sprawling Scarlet</t>
+          <t>Tuần Tra Giấc Mộng: Sprawling Scarlet</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Hạng Chiến Đấu S trong hơn 10 giây</t>
+          <t>Mục tiêu 1: Duy trì Cấp Chiến Đấu S trên 10 giây</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Goal 2: Perform 6 Dodge Counters</t>
+          <t>Mục tiêu 2: Phản đòn 6 lần</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Đánh bại Fractsidus Executioner cuối cùng</t>
+          <t>Mục tiêu 3: Hạ gục Fractsidus Executioner sau cùng</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Dream Patrol: Auto Handpuppet</t>
+          <t>Tuần Tra Giấc Mơ: Bù Nhìn Tự Động</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Hạng Chiến Đấu S</t>
+          <t>Mục tiêu 1: Đạt Cấp Chiến Đấu S</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Goal 2: Perform 4 Dodges</t>
+          <t>Mục tiêu 2: Né 4 lần</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Mục tiêu nút 3: Bị Chop Chop bắt dưới 5 lần</t>
+          <t>Mục tiêu Nút 3: Bị Chop Chop bắt ít hơn 5 lần</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Dream Patrol: Thessaleo Fells</t>
+          <t>Tuần Tra Giấc Mộng: Vách Núi Thessaleo</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Giải cứu Dreamscape Nexus khỏi sự hủy diệt</t>
+          <t>Mục tiêu 1: Bảo vệ Nexus Cảnh Mộng khỏi bị phá hủy</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Dreamscape Nexus trên 30%</t>
+          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 30%</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Dreamscape Nexus trên 60%</t>
+          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 60%</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Dream Patrol: Shattered Heart</t>
+          <t>Tuần Tra Giấc Mộng: Trái Tim Tan Vỡ</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Hạng Chiến Đấu S trong hơn 8 giây</t>
+          <t>Mục tiêu 1: Duy trì Cấp Độ Chiến Đấu S trên 8 giây</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Sử dụng Phản Đòn để phá hủy tất cả vũ khí của Vitreum Dancer</t>
+          <t>Mục tiêu 2: Dùng phản công để phá hủy vũ khí của tất cả Vitreum Dancer</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Dream Patrol: Plushies' Parade</t>
+          <t>Tuần Tra Giấc Mộng: Diễu Hành Thú Nhồi Bông</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Hạng Chiến Đấu S khi thử thách kết thúc</t>
+          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu S khi thử thách kết thúc</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Buộc chấm dứt sự cộng hưởng giữa Cuddle Wuddle và Diggy Duggy</t>
+          <t>Mục tiêu 2: Buộc Cuddle Wuddle và Diggy Duggy chấm dứt cộng hưởng</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Nhận ít hơn 3 cú đánh xẻng từ Diggy Duggy</t>
+          <t>Mục tiêu 3: Chịu ít hơn 3 đòn xẻng từ Diggy Duggy</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Dream Patrol: Hallowed Reach</t>
+          <t>Tuần Tra Giấc Mơ: Cánh Tay Thánh Thiện</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Giải cứu Dreamscape Nexus khỏi sự hủy diệt</t>
+          <t>Mục tiêu 1: Bảo vệ Nexus Cảnh Mộng khỏi bị phá hủy</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Dreamscape Nexus trên 30%</t>
+          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 30%</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Dreamscape Nexus trên 60%</t>
+          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 60%</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Dream Patrol: Forever Bạn bè</t>
+          <t>Tuần Tra Giấc Mơ: Bạn Đồng Hành Vĩnh Cửu</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Hạng Chiến Đấu S trở lên trong 6 giây</t>
+          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu S trở lên trong 6 giây</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Nhận ít hơn 10 đòn đánh</t>
+          <t>Mục tiêu 3: Chịu ít hơn 10 đòn tấn công</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Dream Patrol: Treasured Secrecy</t>
+          <t>Tuần Tra Giấc Mộng: Bí Mật Quý Giá</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Hạng Chiến Đấu SS</t>
+          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu SS</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Sử dụng Phản Đòn để đánh bại 2 Chest Mimic</t>
+          <t>Mục tiêu 2: Dùng phản công đánh bại 2 Chest Mimic</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Không Resonators nào bị hạ gục trong thử thách</t>
+          <t>Mục tiêu 3: No Resonators are downed during the challenge</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Dream Patrol: Hogs of War</t>
+          <t>Tuần Tra Giấc Mơ: Lợn Chiến</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Hạng Chiến Đấu S khi thử thách kết thúc</t>
+          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu S khi thử thách kết thúc</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Làm cho Sabyr Boar choáng bằng cách đâm vào chướng ngại vật 2 lần</t>
+          <t>Mục tiêu 2: Làm cho Lợn Rừng Sabyr đâm vào chướng ngại vật để choáng 2 lần</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Goal 3: Perform 6 Dodges</t>
+          <t>Mục tiêu 3: Né tránh 6 lần</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Dream Patrol: Nimbus Sanctum</t>
+          <t>Tuần Tra Giấc Mộng: Nimbus Sanctum</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Giải cứu Dreamscape Nexus khỏi sự hủy diệt</t>
+          <t>Mục tiêu 1: Bảo vệ Nexus Cảnh Mộng khỏi bị phá hủy</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Giữ Dreamscape Nexus Integrity trên 30%</t>
+          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 30%</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Giữ Dreamscape Nexus Integrity trên 60%</t>
+          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 60%</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Dream Patrol: Bộ đôi cho những kẻ sa ngã</t>
+          <t>Tuần Tra Giấc Mơ: Bản Song Tấu Cho Kẻ Tàn Phai</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Battle Rank S trong hơn 10 giây</t>
+          <t>Mục tiêu 1: Duy trì Cấp Chiến Đấu S trên 10 giây</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Sử dụng Intro Skill 4 lần</t>
+          <t>Mục tiêu 3: Sử dụng Kỹ Năng Khởi Động 4 lần</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Dream Patrol: Spirits Alight</t>
+          <t>Tuần Tra Giấc Mộng: Linh Hồn Bừng Sáng</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Battle Rank SS</t>
+          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu SS</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Ngắt quá trình nạp fireball của Fae Ignis 3 lần</t>
+          <t>Mục tiêu 2: Ngắt nạp đạn lửa của Fae Ignis 3 lần</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Goal 3: Perform 4 Dodges</t>
+          <t>Mục tiêu 3: Né tránh 4 lần</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Dream Patrol: Phù thủy trong đêm thần thánh</t>
+          <t>Tuần Tra Giấc Mộng: Phù Thủy Đêm Linh Thiêng</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Battle Rank S hoặc cao hơn trong 6 giây</t>
+          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu S trở lên trong 6 giây</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Nhận ít hơn 8 lần trúng laser từ Hocus Pocus</t>
+          <t>Mục tiêu 2: Nhận ít hơn 8 đòn laser từ Hocus Pocus</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Đánh bại Cuddle Wuddle cuối cùng</t>
+          <t>Mục tiêu 3: Hạ gục Cuddle Wuddle sau cùng</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Dream Patrol: Penitent's End</t>
+          <t>Tuần Tra Giấc Mộng: Kết Cục Sám Hối</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Giải cứu Dreamscape Nexus khỏi sự hủy diệt</t>
+          <t>Mục tiêu 1: Bảo vệ Nexus Cảnh Mộng khỏi bị phá hủy</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Giữ Dreamscape Nexus Integrity trên 30%</t>
+          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 30%</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Giữ Dreamscape Nexus Integrity trên 60%</t>
+          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 60%</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Battle Rank S trong hơn 10 giây</t>
+          <t>Mục tiêu 1: Duy trì Cấp Chiến Đấu S trên 10 giây</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Goal 2: Perform 8 Dodges</t>
+          <t>Mục tiêu 2: Né 8 lần</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Battle Rank S hoặc cao hơn trong 8 giây</t>
+          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu S trở lên trong 8 giây</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Goal 2: Perform 3 Counterattacks</t>
+          <t>Mục tiêu 2: Thực hiện 3 phản công</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Goal 3: Perform 6 Dodge Counters</t>
+          <t>Mục tiêu 3: Phản đòn né tránh 6 lần</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Battle Rank SS</t>
+          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu SS</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Nhận ít hơn 3 lần trúng từ Diggy Duggies bay do Cuddle Wuddle Dodgem</t>
+          <t>Mục tiêu 2: Nhận ít hơn 3 đòn từ Diggy Duggy bay do Cuddle Wuddle ném</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Giải cứu Dreamscape Nexus khỏi sự hủy diệt</t>
+          <t>Mục tiêu 1: Bảo vệ Nexus Cảnh Mộng khỏi bị phá hủy</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Giữ Dreamscape Nexus Integrity trên 30%</t>
+          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 30%</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Giữ Dreamscape Nexus Integrity trên 60%</t>
+          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 60%</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,8 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Thực hiện 3 lần Phản Đòn làm gián đoạn quá trình tăng cường vũ khí của Knight
-```</t>
+          <t>Mục tiêu 2: Thực hiện 3 phản công làm gián đoạn tăng cường vũ khí của Knight</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23885,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Cấp Chiến Đấu S khi thử thách kết thúc</t>
+          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu S khi thử thách kết thúc</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23955,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Ngắt trạng thái tích năng của Roseshroom bằng cách bắn vào nó</t>
+          <t>Mục tiêu 2: Interrupt the Roseshroom's charging state by shooting it</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24025,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Cấp Chiến Đấu S hoặc cao hơn trong 8 giây</t>
+          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu S trở lên trong 8 giây</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24095,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Không bị trúng vụ nổ Fae Ignis</t>
+          <t>Mục tiêu 2: Don't get caught in the Fae Ignis explosion</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24165,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Defeat Chop Chop last</t>
+          <t>Mục tiêu 3: Hạ gục Chop Chop sau cùng</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24235,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Giải cứu Dreamscape Nexus khỏi sự hủy diệt</t>
+          <t>Mục tiêu 1: Bảo vệ Nexus Cảnh Mộng khỏi bị phá hủy</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24305,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Giữ Độ Toàn Vẹn Dreamscape Nexus trên 30%</t>
+          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 30%</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24375,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Giữ Độ Toàn Vẹn Dreamscape Nexus trên 60%</t>
+          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 60%</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24445,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Cấp Chiến Đấu S hoặc cao hơn trong 8 giây</t>
+          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu S trở lên trong 8 giây</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24515,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Đánh bại Knight trước khi chúng thực hiện 3 lần nâng cấp vũ khí</t>
+          <t>Mục tiêu 2: Tiêu diệt Knight trước khi hắn nâng cấp vũ khí 3 lần</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24585,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Cấp Chiến Đấu SS</t>
+          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu SS</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24725,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Nhận ít hơn 6 đòn đánh</t>
+          <t>Mục tiêu 3: Nhận ít hơn 6 đòn</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24935,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Nhận ít hơn 8 đòn đánh từ Cuddle Wuddle</t>
+          <t>Mục tiêu 3: Nhận ít hơn 8 đòn từ Cuddle Wuddle</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25005,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Cấp Chiến Đấu S hoặc cao hơn trong 8 giây</t>
+          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu S trở lên trong 8 giây</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25075,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Đánh bại 2 Chop Chop liên tiếp trong vòng 15 giây</t>
+          <t>Mục tiêu 2: Tiêu diệt liên tiếp 2 Chop Chop trong vòng 15 giây</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25145,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Goal 3: Perform 6 Dodge Counters</t>
+          <t>Mục tiêu 3: Phản đòn né tránh 6 lần</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25215,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Giải cứu Dreamscape Nexus khỏi sự hủy diệt</t>
+          <t>Mục tiêu 1: Bảo vệ Nexus Cảnh Mộng khỏi bị phá hủy</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25285,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Giữ Độ Toàn Vẹn Dreamscape Nexus trên 30%</t>
+          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 30%</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25355,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Giữ Độ Toàn Vẹn Dreamscape Nexus trên 60%</t>
+          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 60%</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25425,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Cấp Chiến Đấu S hoặc cao hơn trong 6 giây</t>
+          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu S trở lên trong 6 giây</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25495,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Đánh bại 2 Abyssal Patricius liên tiếp trong vòng 10 giây</t>
+          <t>Mục tiêu 2: Tiêu diệt liên tiếp 2 Abyssal Patricius trong vòng 10 giây</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25565,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Bị Freeze ít hơn 2 lần</t>
+          <t>Mục tiêu 3: Bị đóng băng dưới 2 lần</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25635,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Cấp Chiến Đấu S trong hơn 10 giây</t>
+          <t>Mục tiêu 1: Duy trì Cấp Chiến Đấu S trên 10 giây</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25705,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Goal 2: Perform 6 Dodge Counters</t>
+          <t>Mục tiêu 2: Phản đòn 6 lần</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25775,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Đánh bại Fractsidus Executioner cuối cùng</t>
+          <t>Mục tiêu 3: Hạ gục Fractsidus Executioner sau cùng</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25845,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Reach Battle Rank S</t>
+          <t>Mục tiêu 1: Đạt Cấp Chiến Đấu S</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25915,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Goal 2: Perform 4 Dodges</t>
+          <t>Mục tiêu 2: Né 4 lần</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25985,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Mục tiêu nút 3: Bị Chop Chop bắt ít hơn 5 lần</t>
+          <t>Mục tiêu Nút 3: Bị Chop Chop bắt dưới 5 lần</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26055,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Giải cứu Dreamscape Nexus khỏi sự hủy diệt</t>
+          <t>Mục tiêu 1: Bảo vệ Nexus Cảnh Mộng khỏi bị phá hủy</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26125,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Dreamscape Nexus trên 30%</t>
+          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 30%</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26195,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Dreamscape Nexus trên 60%</t>
+          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 60%</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26265,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu S trong hơn 8 giây</t>
+          <t>Mục tiêu 1: Duy trì Cấp Độ Chiến Đấu S trên 8 giây</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26335,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Sử dụng Phản Đòn để phá hủy vũ khí của tất cả Vitreum Dancer</t>
+          <t>Mục tiêu 2: Dùng phản công để phá hủy vũ khí của tất cả Vitreum Dancer</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26405,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Reach Battle Rank S khi thử thách kết thúc</t>
+          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu S khi thử thách kết thúc</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26475,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Buộc chấm dứt sự cộng hưởng giữa Cuddle Wuddle và Diggy Duggy</t>
+          <t>Mục tiêu 2: Buộc Cuddle Wuddle và Diggy Duggy chấm dứt cộng hưởng</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26545,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Chịu ít hơn 3 cú đánh xẻng từ Diggy Duggy</t>
+          <t>Mục tiêu 3: Chịu ít hơn 3 đòn xẻng từ Diggy Duggy</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26615,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Giải cứu Dreamscape Nexus khỏi sự hủy diệt</t>
+          <t>Mục tiêu 1: Bảo vệ Nexus Cảnh Mộng khỏi bị phá hủy</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26685,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Dreamscape Nexus trên 30%</t>
+          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 30%</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26755,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Dreamscape Nexus trên 60%</t>
+          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 60%</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26825,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu S hoặc cao hơn trong 6 giây</t>
+          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu S trở lên trong 6 giây</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26895,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Chịu ít hơn 10 đòn đánh</t>
+          <t>Mục tiêu 3: Chịu ít hơn 10 đòn tấn công</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26965,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Reach Battle Rank SS</t>
+          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu SS</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27035,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Sử dụng Phản Đòn để đánh bại 2 Chest Mimic</t>
+          <t>Mục tiêu 2: Dùng phản công đánh bại 2 Chest Mimic</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27105,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Không có Resonators nào bị hạ gục trong thử thách</t>
+          <t>Mục tiêu 3: No Resonators are downed during the challenge</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27175,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu S khi thử thách kết thúc</t>
+          <t>Mục tiêu 1: Đạt Cấp Chiến Đấu S khi thử thách kết thúc</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27245,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Làm cho Sabyr Boar choáng bằng cách đâm vào chướng ngại vật 2 lần</t>
+          <t>Mục tiêu 2: Làm cho Lợn Rừng Sabyr đâm vào chướng ngại vật để choáng 2 lần</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27315,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Goal 3: Perform 6 Dodges</t>
+          <t>Mục tiêu 3: Né tránh 6 lần</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27385,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Giải cứu Dreamscape Nexus khỏi sự hủy diệt</t>
+          <t>Mục tiêu 1: Bảo vệ Nexus Cảnh Mộng khỏi bị phá hủy</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27455,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Dreamscape Nexus trên 30%</t>
+          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 30%</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27525,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Dreamscape Nexus trên 60%</t>
+          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 60%</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27595,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Reach Battle Rank S trong hơn 10 giây</t>
+          <t>Mục tiêu 1: Duy trì Cấp Chiến Đấu S trên 10 giây</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27665,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Sử dụng Intro Skill 4 lần</t>
+          <t>Mục tiêu 3: Sử dụng Kỹ Năng Khởi Động 4 lần</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27735,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Hạng Chiến Đấu SS</t>
+          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu SS</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27805,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Ngắt nạp lửa của Fae Ignis 3 lần</t>
+          <t>Mục tiêu 2: Ngắt nạp đạn lửa của Fae Ignis 3 lần</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27875,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Goal 3: Perform 4 Dodges</t>
+          <t>Mục tiêu 3: Né tránh 4 lần</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27945,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Hạng Chiến Đấu S trở lên trong 6 giây</t>
+          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu S trở lên trong 6 giây</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28015,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Nhận ít hơn 8 lần trúng tia laser từ Hocus Pocus</t>
+          <t>Mục tiêu 2: Nhận ít hơn 8 đòn laser từ Hocus Pocus</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28085,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Đánh bại Cuddle Wuddle cuối cùng</t>
+          <t>Mục tiêu 3: Hạ gục Cuddle Wuddle sau cùng</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28155,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Cứu Dreamscape Nexus khỏi bị phá hủy</t>
+          <t>Mục tiêu 1: Bảo vệ Nexus Cảnh Mộng khỏi bị phá hủy</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28225,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Giữ Integrity của Dreamscape Nexus trên 30%</t>
+          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 30%</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28295,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Giữ Integrity của Dreamscape Nexus trên 60%</t>
+          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 60%</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28365,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Dream Patrol: Platinum Bladeguard</t>
+          <t>Tuần Tra Giấc Mộng: Kiếm Thánh Bạch Kim</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28435,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Hạng Chiến Đấu S trở lên trong 8 giây</t>
+          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu S trở lên trong 8 giây</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28505,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Goal 2: Perform 2 Counterattacks</t>
+          <t>Mục tiêu 2: Thực hiện 2 phản công</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28575,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Đánh bại hiệp sĩ khi nó bị immobilize</t>
+          <t>Mục tiêu 3: Hạ gục hiệp sĩ khi nó bị bất động</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28645,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Hạng Chiến Đấu S trở lên trong 8 giây</t>
+          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu S trở lên trong 8 giây</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28715,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Goal 2: Perform 2 Counterattacks</t>
+          <t>Mục tiêu 2: Thực hiện 2 phản công</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28785,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Đánh bại hiệp sĩ khi nó bị immobilize</t>
+          <t>Mục tiêu 3: Hạ gục hiệp sĩ khi nó bị bất động</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28855,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Dream Patrol: Gemstone of Desire</t>
+          <t>Tuần Tra Giấc Mơ: Viên Ngọc Của Dục Vọng</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28925,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Hạng Chiến Đấu S trong hơn 10 giây</t>
+          <t>Mục tiêu 1: Duy trì Cấp Chiến Đấu S trên 10 giây</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28995,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Immobilize Rage against the Statue 2 lần</t>
+          <t>Mục tiêu 2: Khóa chuyển động của Rage against the Statue 2 lần</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29065,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Nhận ít hơn 10 lần trúng đòn</t>
+          <t>Mục tiêu 3: Chịu ít hơn 10 đòn tấn công</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29135,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Hạng Chiến Đấu S trong hơn 10 giây</t>
+          <t>Mục tiêu 1: Duy trì Cấp Chiến Đấu S trên 10 giây</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29205,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Immobilize Rage against the Statue 2 lần</t>
+          <t>Mục tiêu 2: Khóa chuyển động của Rage against the Statue 2 lần</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29275,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Nhận ít hơn 10 lần trúng đòn</t>
+          <t>Mục tiêu 3: Chịu ít hơn 10 đòn tấn công</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29345,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Dreamscape Node: Land Rồng</t>
+          <t>Nút Giấc Mơ: Vùng Đất Rồng</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29415,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Hạng Chiến Đấu S khi thử thách kết thúc</t>
+          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu S khi thử thách kết thúc</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29485,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Bị đóng băng ít hơn 2 lần</t>
+          <t>Mục tiêu 2: Bị đóng băng dưới 2 lần</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29555,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Goal 3: Perform 3 Dodges</t>
+          <t>Mục tiêu 3: Né tránh 3 lần</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29625,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Dreamscape Node: Land Kiếm Thuật</t>
+          <t>Mảnh Giấc Mơ: Vùng Đất Kiếm Khách</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29695,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Goal 1: Perform 4 Dodge Counters</t>
+          <t>Mục tiêu 1: Thực hiện 4 Né Phản Công</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29765,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Attack Capitaneus từ phía sau để immobilize nó 1 lần</t>
+          <t>Mục tiêu 2: Tấn công Capitaneus từ phía sau để khiến nó bất động một lần</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29835,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Nhận ít hơn 10 đòn từ Sagittario</t>
+          <t>Mục tiêu 3: Chịu ít hơn 10 đòn tấn công từ Sagittario</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29905,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Dreamscape Node: Land of Unity</t>
+          <t>Mảnh Giấc Mơ: Vùng Đất Đoàn Kết</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29975,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Goal 1: Perform 2 Counterattacks</t>
+          <t>Mục tiêu 1: Thực hiện 2 Phản Đòn</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30045,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Avinoleum Dreamscape Nexus</t>
+          <t>Mạch Mộng Cảnh Avinoleum</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30115,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Giải cứu Dreamscape Nexus khỏi sự hủy diệt</t>
+          <t>Mục tiêu 1: Bảo vệ Nexus Cảnh Mộng khỏi bị phá hủy</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30185,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Dreamscape Nexus trên 30%</t>
+          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 30%</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30255,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Dreamscape Nexus trên 60%</t>
+          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 60%</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30325,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Hạng Chiến Đấu S khi thử thách kết thúc</t>
+          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu S khi thử thách kết thúc</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30395,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Bị đóng băng ít hơn 2 lần</t>
+          <t>Mục tiêu 2: Bị đóng băng dưới 2 lần</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30465,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Goal 3: Perform 3 Dodges</t>
+          <t>Mục tiêu 3: Né tránh 3 lần</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30535,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Goal 1: Perform 4 Dodge Counters</t>
+          <t>Mục tiêu 1: Thực hiện 4 Né Phản Công</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30605,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Attack Capitaneus từ phía sau để bất động nó một lần</t>
+          <t>Mục tiêu 2: Tấn công Capitaneus từ phía sau để khiến nó bất động một lần</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30675,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Nhận ít hơn 10 đòn từ Sagittario</t>
+          <t>Mục tiêu 3: Chịu ít hơn 10 đòn tấn công từ Sagittario</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30745,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Goal 1: Perform 2 Counterattacks</t>
+          <t>Mục tiêu 1: Thực hiện 2 Phản Đòn</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30815,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Giải cứu Dreamscape Nexus khỏi sự hủy diệt</t>
+          <t>Mục tiêu 1: Bảo vệ Nexus Cảnh Mộng khỏi bị phá hủy</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30885,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Dreamscape Nexus trên 30%</t>
+          <t>Mục tiêu 2: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 30%</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30955,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Dreamscape Nexus trên 60%</t>
+          <t>Mục tiêu 3: Duy trì Độ Toàn Vẹn Mạng Lưới Giấc Mơ trên 60%</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31025,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Goal 1: Perform 6 Dodge Counters</t>
+          <t>Mục tiêu 1: Thực hiện 6 Né Phản Công</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31095,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Bất động Pilgrim's Shell</t>
+          <t>Mục tiêu 2: Khóa chuyển động của Pilgrim's Shell</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31165,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Tránh bị mắc kẹt bởi san hô</t>
+          <t>Mục tiêu 3: Tránh bị san hô mắc kẹt</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31235,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Dream Contagion: Tàn Tích Của Vỏ Ốc</t>
+          <t>Ác Mộng Truyền Nhiễm: Tàn Tích Vỏ Ốc</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31305,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Goal 1: Perform 6 Dodge Counters</t>
+          <t>Mục tiêu 1: Thực hiện 6 Né Phản Công</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31375,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Mục tiêu 2: Bất động Pilgrim's Shell</t>
+          <t>Mục tiêu 2: Khóa chuyển động của Pilgrim's Shell</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31445,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Tránh bị mắc kẹt bởi san hô</t>
+          <t>Mục tiêu 3: Tránh bị san hô mắc kẹt</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31515,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Hạng Chiến Đấu SS</t>
+          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu SS</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31725,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Dream Contagion: Ba Con Hổ Của Septimont</t>
+          <t>Ác Mộng Truyền Nhiễm: Tam Hổ Septimont</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31795,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt Hạng Chiến Đấu SS</t>
+          <t>Mục tiêu 1: Đạt Cấp Độ Chiến Đấu SS</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -32005,8 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Đạt và duy trì Hạng Chiến Đấu SS hoặc cao hơn trong 10 giây
-```</t>
+          <t>Mục tiêu 1: Đạt và duy trì Cấp Độ Chiến Đấu SS trở lên trong 10 giây</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32076,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Goal 2: Perform 2 Counterattacks</t>
+          <t>Mục tiêu 2: Thực hiện 2 phản công</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32146,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Không bị trúng đá do Kerasaur Dodgem</t>
+          <t>Mục tiêu 3: Không bị trúng đá do Kerasaur ném</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32216,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Dream Contagion: Savage Outrider</t>
+          <t>Ác Mộng Truyền Nhiễm: Kỵ Sĩ Hoang Dã</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32356,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Goal 2: Perform 2 Counterattacks</t>
+          <t>Mục tiêu 2: Thực hiện 2 phản công</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32426,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Không bị trúng đá do Kerasaur Dodgem</t>
+          <t>Mục tiêu 3: Không bị trúng đá do Kerasaur ném</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32496,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Reach Battle Rank SS trong hơn 10 giây</t>
+          <t>Mục tiêu 1: Duy trì Cấp Độ Chiến Đấu SS trên 10 giây</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32566,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Goal 2: Perform 8 Dodges</t>
+          <t>Mục tiêu 2: Né 8 lần</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32636,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Tránh bị trúng các đòn tấn công phối hợp của Drakes</t>
+          <t>Mục tiêu 3: Tránh né các đòn phối hợp của bầy Drake</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32706,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Dream Contagion: Ultimate Winged Dragon</t>
+          <t>Ác Mộng Truyền Nhiễm: Rồng Cánh Tối Thượng</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32776,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Mục tiêu 1: Reach Battle Rank SS trong hơn 10 giây</t>
+          <t>Mục tiêu 1: Duy trì Cấp Độ Chiến Đấu SS trên 10 giây</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32846,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Goal 2: Perform 8 Dodges</t>
+          <t>Mục tiêu 2: Né 8 lần</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32916,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Mục tiêu 3: Tránh bị trúng các đòn tấn công phối hợp của Drakes</t>
+          <t>Mục tiêu 3: Tránh né các đòn phối hợp của bầy Drake</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32986,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Dreams of Cindertide: Blood</t>
+          <t>Giấc Mơ Của Tro Tàn: Huyết</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33056,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Dreams of Cindertide: Bone</t>
+          <t>Giấc Mơ Tro Tàn: Cốt</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33126,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Dreams of Cindertide: Animus</t>
+          <t>Giấc Mơ Của Tro Tàn: Animus</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33196,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Dreams of Cindertide: Finale</t>
+          <t>Giấc Mơ Tro Tàn: Khúc Kết</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33266,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Mục tiêu thử thách</t>
+          <t>Mục Tiêu Thách Đấu</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33336,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Challenge Rules</t>
+          <t>Quy Tắc Thử Thách</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33476,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Dreams of Cindertide: Blood</t>
+          <t>Giấc Mơ Của Tro Tàn: Huyết</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33546,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Thử thách I</t>
+          <t>Thử Thách I</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33616,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Thử thách II</t>
+          <t>Thử Thách II</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33686,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Thử thách III</t>
+          <t>Thử Thách III</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33756,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Dreams of Cindertide: Bone</t>
+          <t>Giấc Mơ Tro Tàn: Cốt</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33826,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Thử thách I</t>
+          <t>Thử Thách I</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33896,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Thử thách II</t>
+          <t>Thử Thách II</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33966,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Thử thách III</t>
+          <t>Thử Thách III</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34036,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Dreams of Cindertide: Animus</t>
+          <t>Giấc Mơ Của Tro Tàn: Animus</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34106,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Thử thách I</t>
+          <t>Thử Thách I</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34176,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Thử thách II</t>
+          <t>Thử Thách II</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34246,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Challenge III</t>
+          <t>Thử Thách III</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34316,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Dreams of Cindertide: Phần Kết</t>
+          <t>Giấc Mơ Tro Tàn: Khúc Kết</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34386,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Challenge I</t>
+          <t>Thử Thách I</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34456,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Challenge II</t>
+          <t>Thử Thách II</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34526,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Challenge III</t>
+          <t>Thử Thách III</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34596,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Treasure Spot</t>
+          <t>Điểm Kho Báu</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34666,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Treasure Spot</t>
+          <t>Điểm Kho Báu</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34736,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Treasure Spot</t>
+          <t>Điểm Kho Báu</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34806,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Treasure Spot</t>
+          <t>Điểm Kho Báu</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34876,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Treasure Spot</t>
+          <t>Điểm Kho Báu</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34946,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Treasure Spot</t>
+          <t>Điểm Kho Báu</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35016,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Treasure Spot</t>
+          <t>Điểm Kho Báu</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35086,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Treasure Spot</t>
+          <t>Điểm Kho Báu</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35156,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Treasure Spot</t>
+          <t>Điểm Kho Báu</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
